--- a/artfynd/A 16956-2026 artfynd.xlsx
+++ b/artfynd/A 16956-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132267076</v>
       </c>
       <c r="B2" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>132267059</v>
       </c>
       <c r="B3" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16956-2026 artfynd.xlsx
+++ b/artfynd/A 16956-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132267076</v>
       </c>
       <c r="B2" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>132267059</v>
       </c>
       <c r="B3" t="n">
-        <v>58492</v>
+        <v>58493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16956-2026 artfynd.xlsx
+++ b/artfynd/A 16956-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132267076</v>
       </c>
       <c r="B2" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>132267059</v>
       </c>
       <c r="B3" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16956-2026 artfynd.xlsx
+++ b/artfynd/A 16956-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132267076</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>132267059</v>
       </c>
       <c r="B3" t="n">
-        <v>58497</v>
+        <v>58498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16956-2026 artfynd.xlsx
+++ b/artfynd/A 16956-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132267076</v>
+        <v>132267059</v>
       </c>
       <c r="B2" t="n">
-        <v>58115</v>
+        <v>58519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579294</v>
+        <v>579312</v>
       </c>
       <c r="R2" t="n">
-        <v>6413199</v>
+        <v>6413212</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,7 +776,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Läte veriferat med Merlin Bird App</t>
+          <t>Sången verifierad även med Merlin Bird App</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,32 +803,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132267059</v>
+        <v>132267076</v>
       </c>
       <c r="B3" t="n">
-        <v>58498</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,7 +840,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579312</v>
+        <v>579294</v>
       </c>
       <c r="R3" t="n">
-        <v>6413212</v>
+        <v>6413199</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sången verifierad även med Merlin Bird App</t>
+          <t>Läte veriferat med Merlin Bird App</t>
         </is>
       </c>
       <c r="AD3" t="b">
